--- a/morphopasse-calibration/data/raw/raw_Data_morpho.xlsx
+++ b/morphopasse-calibration/data/raw/raw_Data_morpho.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joseph_Hefner\Desktop\buRns_morphoPASSe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\Desktop\buRns_morphoPASSe\data analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE57D83-ADC3-4287-9255-5B23B154E7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="32190" windowHeight="13260"/>
+    <workbookView xWindow="5160" yWindow="270" windowWidth="31260" windowHeight="20730" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="simulated cranial data" sheetId="1" r:id="rId1"/>
@@ -74,160 +75,10 @@
     <t>Balanced</t>
   </si>
   <si>
-    <t>Morp1</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
-    <t>Morp2</t>
-  </si>
-  <si>
     <t>F</t>
-  </si>
-  <si>
-    <t>Morp3</t>
-  </si>
-  <si>
-    <t>Morp4</t>
-  </si>
-  <si>
-    <t>Morp5</t>
-  </si>
-  <si>
-    <t>Morp6</t>
-  </si>
-  <si>
-    <t>Morp7</t>
-  </si>
-  <si>
-    <t>Morp8</t>
-  </si>
-  <si>
-    <t>Morp9</t>
-  </si>
-  <si>
-    <t>Morp10</t>
-  </si>
-  <si>
-    <t>Morp11</t>
-  </si>
-  <si>
-    <t>Morp12</t>
-  </si>
-  <si>
-    <t>Morp13</t>
-  </si>
-  <si>
-    <t>Morp14</t>
-  </si>
-  <si>
-    <t>Morp15</t>
-  </si>
-  <si>
-    <t>Morp16</t>
-  </si>
-  <si>
-    <t>Morp17</t>
-  </si>
-  <si>
-    <t>Morp18</t>
-  </si>
-  <si>
-    <t>Morp19</t>
-  </si>
-  <si>
-    <t>Morp20</t>
-  </si>
-  <si>
-    <t>Morp21</t>
-  </si>
-  <si>
-    <t>Morp22</t>
-  </si>
-  <si>
-    <t>Morp23</t>
-  </si>
-  <si>
-    <t>Morp24</t>
-  </si>
-  <si>
-    <t>Morp25</t>
-  </si>
-  <si>
-    <t>Morp26</t>
-  </si>
-  <si>
-    <t>Morp27</t>
-  </si>
-  <si>
-    <t>Morp28</t>
-  </si>
-  <si>
-    <t>Morp29</t>
-  </si>
-  <si>
-    <t>Morp30</t>
-  </si>
-  <si>
-    <t>Morp31</t>
-  </si>
-  <si>
-    <t>Morp32</t>
-  </si>
-  <si>
-    <t>Morp33</t>
-  </si>
-  <si>
-    <t>Morp34</t>
-  </si>
-  <si>
-    <t>Morp35</t>
-  </si>
-  <si>
-    <t>Morp36</t>
-  </si>
-  <si>
-    <t>Morp37</t>
-  </si>
-  <si>
-    <t>Morp38</t>
-  </si>
-  <si>
-    <t>Morp39</t>
-  </si>
-  <si>
-    <t>Morp40</t>
-  </si>
-  <si>
-    <t>Morp41</t>
-  </si>
-  <si>
-    <t>Morp42</t>
-  </si>
-  <si>
-    <t>Morp43</t>
-  </si>
-  <si>
-    <t>Morp44</t>
-  </si>
-  <si>
-    <t>Morp45</t>
-  </si>
-  <si>
-    <t>Morp46</t>
-  </si>
-  <si>
-    <t>Morp47</t>
-  </si>
-  <si>
-    <t>Morp48</t>
-  </si>
-  <si>
-    <t>Morp49</t>
-  </si>
-  <si>
-    <t>Morp50</t>
   </si>
   <si>
     <t>MAL</t>
@@ -334,11 +185,161 @@
   <si>
     <t>postprob</t>
   </si>
+  <si>
+    <t>SIM001</t>
+  </si>
+  <si>
+    <t>SIM002</t>
+  </si>
+  <si>
+    <t>SIM003</t>
+  </si>
+  <si>
+    <t>SIM004</t>
+  </si>
+  <si>
+    <t>SIM005</t>
+  </si>
+  <si>
+    <t>SIM006</t>
+  </si>
+  <si>
+    <t>SIM007</t>
+  </si>
+  <si>
+    <t>SIM008</t>
+  </si>
+  <si>
+    <t>SIM009</t>
+  </si>
+  <si>
+    <t>SIM010</t>
+  </si>
+  <si>
+    <t>SIM011</t>
+  </si>
+  <si>
+    <t>SIM012</t>
+  </si>
+  <si>
+    <t>SIM013</t>
+  </si>
+  <si>
+    <t>SIM014</t>
+  </si>
+  <si>
+    <t>SIM015</t>
+  </si>
+  <si>
+    <t>SIM016</t>
+  </si>
+  <si>
+    <t>SIM017</t>
+  </si>
+  <si>
+    <t>SIM018</t>
+  </si>
+  <si>
+    <t>SIM019</t>
+  </si>
+  <si>
+    <t>SIM020</t>
+  </si>
+  <si>
+    <t>SIM021</t>
+  </si>
+  <si>
+    <t>SIM022</t>
+  </si>
+  <si>
+    <t>SIM023</t>
+  </si>
+  <si>
+    <t>SIM024</t>
+  </si>
+  <si>
+    <t>SIM025</t>
+  </si>
+  <si>
+    <t>SIM026</t>
+  </si>
+  <si>
+    <t>SIM027</t>
+  </si>
+  <si>
+    <t>SIM028</t>
+  </si>
+  <si>
+    <t>SIM029</t>
+  </si>
+  <si>
+    <t>SIM030</t>
+  </si>
+  <si>
+    <t>SIM031</t>
+  </si>
+  <si>
+    <t>SIM032</t>
+  </si>
+  <si>
+    <t>SIM033</t>
+  </si>
+  <si>
+    <t>SIM034</t>
+  </si>
+  <si>
+    <t>SIM035</t>
+  </si>
+  <si>
+    <t>SIM036</t>
+  </si>
+  <si>
+    <t>SIM037</t>
+  </si>
+  <si>
+    <t>SIM038</t>
+  </si>
+  <si>
+    <t>SIM039</t>
+  </si>
+  <si>
+    <t>SIM040</t>
+  </si>
+  <si>
+    <t>SIM041</t>
+  </si>
+  <si>
+    <t>SIM042</t>
+  </si>
+  <si>
+    <t>SIM043</t>
+  </si>
+  <si>
+    <t>SIM044</t>
+  </si>
+  <si>
+    <t>SIM045</t>
+  </si>
+  <si>
+    <t>SIM046</t>
+  </si>
+  <si>
+    <t>SIM047</t>
+  </si>
+  <si>
+    <t>SIM048</t>
+  </si>
+  <si>
+    <t>SIM049</t>
+  </si>
+  <si>
+    <t>SIM050</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -649,7 +650,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P51"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -684,7 +685,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -710,31 +711,31 @@
     </row>
     <row r="2" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I2">
-        <v>0.99199999999999999</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="J2">
         <v>0.83169999999999999</v>
@@ -760,31 +761,31 @@
     </row>
     <row r="3" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I3">
-        <v>0.91400000000000003</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="J3">
         <v>0.83169999999999999</v>
@@ -810,31 +811,31 @@
     </row>
     <row r="4" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="J4">
         <v>0.83169999999999999</v>
@@ -860,31 +861,31 @@
     </row>
     <row r="5" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I5">
-        <v>0.56200000000000006</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0.83169999999999999</v>
@@ -910,31 +911,31 @@
     </row>
     <row r="6" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I6">
-        <v>0.70599999999999996</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="J6">
         <v>0.83169999999999999</v>
@@ -960,31 +961,31 @@
     </row>
     <row r="7" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>0.94799999999999995</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0.83169999999999999</v>
@@ -1010,31 +1011,31 @@
     </row>
     <row r="8" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8">
-        <v>0.998</v>
+        <v>0.68</v>
       </c>
       <c r="J8">
         <v>0.83169999999999999</v>
@@ -1060,31 +1061,31 @@
     </row>
     <row r="9" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
         <v>3</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I9">
-        <v>0.74</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="J9">
         <v>0.83169999999999999</v>
@@ -1110,31 +1111,31 @@
     </row>
     <row r="10" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10">
-        <v>0.874</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0.83169999999999999</v>
@@ -1160,31 +1161,31 @@
     </row>
     <row r="11" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I11">
-        <v>0.54</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="J11">
         <v>0.83169999999999999</v>
@@ -1210,31 +1211,31 @@
     </row>
     <row r="12" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I12">
-        <v>0.73799999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="J12">
         <v>0.83169999999999999</v>
@@ -1243,7 +1244,7 @@
         <v>0.6633</v>
       </c>
       <c r="L12">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M12">
         <v>0.84330000000000005</v>
@@ -1260,19 +1261,19 @@
     </row>
     <row r="13" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>3</v>
@@ -1281,10 +1282,10 @@
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I13">
-        <v>0.69599999999999995</v>
+        <v>0.85799999999999998</v>
       </c>
       <c r="J13">
         <v>0.83169999999999999</v>
@@ -1293,7 +1294,7 @@
         <v>0.6633</v>
       </c>
       <c r="L13">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M13">
         <v>0.84330000000000005</v>
@@ -1310,31 +1311,31 @@
     </row>
     <row r="14" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="J14">
         <v>0.83169999999999999</v>
@@ -1343,7 +1344,7 @@
         <v>0.6633</v>
       </c>
       <c r="L14">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M14">
         <v>0.84330000000000005</v>
@@ -1360,31 +1361,31 @@
     </row>
     <row r="15" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15">
         <v>4</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I15">
-        <v>0.98399999999999999</v>
+        <v>0.996</v>
       </c>
       <c r="J15">
         <v>0.83169999999999999</v>
@@ -1393,7 +1394,7 @@
         <v>0.6633</v>
       </c>
       <c r="L15">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M15">
         <v>0.84330000000000005</v>
@@ -1410,28 +1411,28 @@
     </row>
     <row r="16" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>4</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -1443,7 +1444,7 @@
         <v>0.6633</v>
       </c>
       <c r="L16">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M16">
         <v>0.84330000000000005</v>
@@ -1460,31 +1461,31 @@
     </row>
     <row r="17" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I17">
-        <v>0.90400000000000003</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0.83169999999999999</v>
@@ -1493,7 +1494,7 @@
         <v>0.6633</v>
       </c>
       <c r="L17">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M17">
         <v>0.84330000000000005</v>
@@ -1510,7 +1511,7 @@
     </row>
     <row r="18" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -1519,22 +1520,22 @@
         <v>4</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I18">
-        <v>0.84799999999999998</v>
+        <v>0.504</v>
       </c>
       <c r="J18">
         <v>0.83169999999999999</v>
@@ -1543,7 +1544,7 @@
         <v>0.6633</v>
       </c>
       <c r="L18">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M18">
         <v>0.84330000000000005</v>
@@ -1560,31 +1561,31 @@
     </row>
     <row r="19" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I19">
-        <v>0.82</v>
+        <v>0.85799999999999998</v>
       </c>
       <c r="J19">
         <v>0.83169999999999999</v>
@@ -1593,7 +1594,7 @@
         <v>0.6633</v>
       </c>
       <c r="L19">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M19">
         <v>0.84330000000000005</v>
@@ -1610,13 +1611,13 @@
     </row>
     <row r="20" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -1625,16 +1626,16 @@
         <v>3</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I20">
-        <v>0.96399999999999997</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="J20">
         <v>0.83169999999999999</v>
@@ -1643,10 +1644,10 @@
         <v>0.6633</v>
       </c>
       <c r="L20">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M20">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000105</v>
       </c>
       <c r="N20">
         <v>0.83960000000000001</v>
@@ -1660,31 +1661,31 @@
     </row>
     <row r="21" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21">
         <v>4</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I21">
-        <v>0.67</v>
+        <v>0.998</v>
       </c>
       <c r="J21">
         <v>0.83169999999999999</v>
@@ -1693,10 +1694,10 @@
         <v>0.6633</v>
       </c>
       <c r="L21">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M21">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000105</v>
       </c>
       <c r="N21">
         <v>0.83960000000000001</v>
@@ -1710,31 +1711,31 @@
     </row>
     <row r="22" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F22">
         <v>4</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I22">
-        <v>0.71599999999999997</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="J22">
         <v>0.83169999999999999</v>
@@ -1743,10 +1744,10 @@
         <v>0.6633</v>
       </c>
       <c r="L22">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M22">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000105</v>
       </c>
       <c r="N22">
         <v>0.83960000000000001</v>
@@ -1760,31 +1761,31 @@
     </row>
     <row r="23" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I23">
-        <v>0.98599999999999999</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="J23">
         <v>0.83169999999999999</v>
@@ -1793,10 +1794,10 @@
         <v>0.6633</v>
       </c>
       <c r="L23">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M23">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000105</v>
       </c>
       <c r="N23">
         <v>0.83960000000000001</v>
@@ -1810,10 +1811,10 @@
     </row>
     <row r="24" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -1822,19 +1823,19 @@
         <v>3</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
       </c>
       <c r="I24">
-        <v>0.84</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="J24">
         <v>0.83169999999999999</v>
@@ -1843,10 +1844,10 @@
         <v>0.6633</v>
       </c>
       <c r="L24">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M24">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000205</v>
       </c>
       <c r="N24">
         <v>0.83960000000000001</v>
@@ -1860,31 +1861,31 @@
     </row>
     <row r="25" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25">
         <v>3</v>
       </c>
       <c r="H25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I25">
-        <v>0.98199999999999998</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="J25">
         <v>0.83169999999999999</v>
@@ -1893,10 +1894,10 @@
         <v>0.6633</v>
       </c>
       <c r="L25">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M25">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000205</v>
       </c>
       <c r="N25">
         <v>0.83960000000000001</v>
@@ -1910,31 +1911,31 @@
     </row>
     <row r="26" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H26" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I26">
-        <v>0.97599999999999998</v>
+        <v>0.94199999999999995</v>
       </c>
       <c r="J26">
         <v>0.83169999999999999</v>
@@ -1943,10 +1944,10 @@
         <v>0.6633</v>
       </c>
       <c r="L26">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M26">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000205</v>
       </c>
       <c r="N26">
         <v>0.83960000000000001</v>
@@ -1960,31 +1961,31 @@
     </row>
     <row r="27" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27">
         <v>3</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I27">
-        <v>0.96399999999999997</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="J27">
         <v>0.83169999999999999</v>
@@ -1993,10 +1994,10 @@
         <v>0.6633</v>
       </c>
       <c r="L27">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M27">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000205</v>
       </c>
       <c r="N27">
         <v>0.83960000000000001</v>
@@ -2010,31 +2011,31 @@
     </row>
     <row r="28" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I28">
-        <v>0.82799999999999996</v>
+        <v>0.998</v>
       </c>
       <c r="J28">
         <v>0.83169999999999999</v>
@@ -2043,10 +2044,10 @@
         <v>0.6633</v>
       </c>
       <c r="L28">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M28">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000205</v>
       </c>
       <c r="N28">
         <v>0.83960000000000001</v>
@@ -2060,31 +2061,31 @@
     </row>
     <row r="29" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I29">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="J29">
         <v>0.83169999999999999</v>
@@ -2093,10 +2094,10 @@
         <v>0.6633</v>
       </c>
       <c r="L29">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M29">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000205</v>
       </c>
       <c r="N29">
         <v>0.83960000000000001</v>
@@ -2110,31 +2111,31 @@
     </row>
     <row r="30" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I30">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0.83169999999999999</v>
@@ -2143,10 +2144,10 @@
         <v>0.6633</v>
       </c>
       <c r="L30">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M30">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000205</v>
       </c>
       <c r="N30">
         <v>0.83960000000000001</v>
@@ -2160,31 +2161,31 @@
     </row>
     <row r="31" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I31">
-        <v>0.73799999999999999</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="J31">
         <v>0.83169999999999999</v>
@@ -2193,10 +2194,10 @@
         <v>0.6633</v>
       </c>
       <c r="L31">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M31">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000205</v>
       </c>
       <c r="N31">
         <v>0.83960000000000001</v>
@@ -2210,31 +2211,31 @@
     </row>
     <row r="32" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I32">
-        <v>0.94799999999999995</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="J32">
         <v>0.83169999999999999</v>
@@ -2243,10 +2244,10 @@
         <v>0.6633</v>
       </c>
       <c r="L32">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M32">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000305</v>
       </c>
       <c r="N32">
         <v>0.83960000000000001</v>
@@ -2260,19 +2261,19 @@
     </row>
     <row r="33" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -2281,10 +2282,10 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I33">
-        <v>0.60199999999999998</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J33">
         <v>0.83169999999999999</v>
@@ -2293,10 +2294,10 @@
         <v>0.6633</v>
       </c>
       <c r="L33">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M33">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000305</v>
       </c>
       <c r="N33">
         <v>0.83960000000000001</v>
@@ -2310,31 +2311,31 @@
     </row>
     <row r="34" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I34">
-        <v>0.998</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="J34">
         <v>0.83169999999999999</v>
@@ -2343,10 +2344,10 @@
         <v>0.6633</v>
       </c>
       <c r="L34">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M34">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000305</v>
       </c>
       <c r="N34">
         <v>0.83960000000000001</v>
@@ -2360,31 +2361,31 @@
     </row>
     <row r="35" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I35">
-        <v>0.90400000000000003</v>
+        <v>0.91</v>
       </c>
       <c r="J35">
         <v>0.83169999999999999</v>
@@ -2393,10 +2394,10 @@
         <v>0.6633</v>
       </c>
       <c r="L35">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M35">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000305</v>
       </c>
       <c r="N35">
         <v>0.83960000000000001</v>
@@ -2410,7 +2411,7 @@
     </row>
     <row r="36" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="B36">
         <v>2</v>
@@ -2419,22 +2420,22 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I36">
-        <v>0.90200000000000002</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="J36">
         <v>0.83169999999999999</v>
@@ -2443,10 +2444,10 @@
         <v>0.6633</v>
       </c>
       <c r="L36">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M36">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000305</v>
       </c>
       <c r="N36">
         <v>0.83960000000000001</v>
@@ -2460,31 +2461,31 @@
     </row>
     <row r="37" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37">
-        <v>0.98799999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="J37">
         <v>0.83169999999999999</v>
@@ -2493,10 +2494,10 @@
         <v>0.6633</v>
       </c>
       <c r="L37">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M37">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000305</v>
       </c>
       <c r="N37">
         <v>0.83960000000000001</v>
@@ -2510,13 +2511,13 @@
     </row>
     <row r="38" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -2525,16 +2526,16 @@
         <v>5</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I38">
-        <v>0.81399999999999995</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="J38">
         <v>0.83169999999999999</v>
@@ -2543,10 +2544,10 @@
         <v>0.6633</v>
       </c>
       <c r="L38">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M38">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000305</v>
       </c>
       <c r="N38">
         <v>0.83960000000000001</v>
@@ -2560,31 +2561,31 @@
     </row>
     <row r="39" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I39">
-        <v>0.69399999999999995</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="J39">
         <v>0.83169999999999999</v>
@@ -2593,10 +2594,10 @@
         <v>0.6633</v>
       </c>
       <c r="L39">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M39">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000405</v>
       </c>
       <c r="N39">
         <v>0.83960000000000001</v>
@@ -2610,31 +2611,31 @@
     </row>
     <row r="40" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40">
         <v>4</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I40">
-        <v>0.91800000000000004</v>
+        <v>0.94199999999999995</v>
       </c>
       <c r="J40">
         <v>0.83169999999999999</v>
@@ -2643,10 +2644,10 @@
         <v>0.6633</v>
       </c>
       <c r="L40">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M40">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000405</v>
       </c>
       <c r="N40">
         <v>0.83960000000000001</v>
@@ -2660,10 +2661,10 @@
     </row>
     <row r="41" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -2672,19 +2673,19 @@
         <v>2</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41">
         <v>3</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I41">
-        <v>0.58599999999999997</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="J41">
         <v>0.83169999999999999</v>
@@ -2693,10 +2694,10 @@
         <v>0.6633</v>
       </c>
       <c r="L41">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M41">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000405</v>
       </c>
       <c r="N41">
         <v>0.83960000000000001</v>
@@ -2710,31 +2711,31 @@
     </row>
     <row r="42" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>0.76600000000000001</v>
       </c>
       <c r="J42">
         <v>0.83169999999999999</v>
@@ -2743,10 +2744,10 @@
         <v>0.6633</v>
       </c>
       <c r="L42">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M42">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000405</v>
       </c>
       <c r="N42">
         <v>0.83960000000000001</v>
@@ -2760,31 +2761,31 @@
     </row>
     <row r="43" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I43">
-        <v>0.73799999999999999</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="J43">
         <v>0.83169999999999999</v>
@@ -2793,10 +2794,10 @@
         <v>0.6633</v>
       </c>
       <c r="L43">
-        <v>0.82</v>
+        <v>0.81999999999999895</v>
       </c>
       <c r="M43">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000405</v>
       </c>
       <c r="N43">
         <v>0.83960000000000001</v>
@@ -2810,31 +2811,31 @@
     </row>
     <row r="44" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="J44">
         <v>0.83169999999999999</v>
@@ -2843,10 +2844,10 @@
         <v>0.6633</v>
       </c>
       <c r="L44">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M44">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000405</v>
       </c>
       <c r="N44">
         <v>0.83960000000000001</v>
@@ -2860,25 +2861,25 @@
     </row>
     <row r="45" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -2893,10 +2894,10 @@
         <v>0.6633</v>
       </c>
       <c r="L45">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M45">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000405</v>
       </c>
       <c r="N45">
         <v>0.83960000000000001</v>
@@ -2910,31 +2911,31 @@
     </row>
     <row r="46" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46">
         <v>3</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I46">
-        <v>0.56599999999999995</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="J46">
         <v>0.83169999999999999</v>
@@ -2943,10 +2944,10 @@
         <v>0.6633</v>
       </c>
       <c r="L46">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M46">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000405</v>
       </c>
       <c r="N46">
         <v>0.83960000000000001</v>
@@ -2960,31 +2961,31 @@
     </row>
     <row r="47" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47">
         <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I47">
-        <v>0.97199999999999998</v>
+        <v>0.996</v>
       </c>
       <c r="J47">
         <v>0.83169999999999999</v>
@@ -2993,10 +2994,10 @@
         <v>0.6633</v>
       </c>
       <c r="L47">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M47">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000505</v>
       </c>
       <c r="N47">
         <v>0.83960000000000001</v>
@@ -3010,31 +3011,31 @@
     </row>
     <row r="48" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I48">
-        <v>0.81</v>
+        <v>0.996</v>
       </c>
       <c r="J48">
         <v>0.83169999999999999</v>
@@ -3043,10 +3044,10 @@
         <v>0.6633</v>
       </c>
       <c r="L48">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M48">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000505</v>
       </c>
       <c r="N48">
         <v>0.83960000000000001</v>
@@ -3060,7 +3061,7 @@
     </row>
     <row r="49" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B49">
         <v>3</v>
@@ -3069,22 +3070,22 @@
         <v>4</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49">
         <v>3</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I49">
-        <v>0.76600000000000001</v>
+        <v>0.996</v>
       </c>
       <c r="J49">
         <v>0.83169999999999999</v>
@@ -3093,10 +3094,10 @@
         <v>0.6633</v>
       </c>
       <c r="L49">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M49">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000505</v>
       </c>
       <c r="N49">
         <v>0.83960000000000001</v>
@@ -3110,28 +3111,28 @@
     </row>
     <row r="50" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I50">
         <v>1</v>
@@ -3143,10 +3144,10 @@
         <v>0.6633</v>
       </c>
       <c r="L50">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M50">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000505</v>
       </c>
       <c r="N50">
         <v>0.83960000000000001</v>
@@ -3160,19 +3161,19 @@
     </row>
     <row r="51" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F51">
         <v>2</v>
@@ -3181,10 +3182,10 @@
         <v>2</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I51">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="J51">
         <v>0.83169999999999999</v>
@@ -3193,10 +3194,10 @@
         <v>0.6633</v>
       </c>
       <c r="L51">
-        <v>0.82</v>
+        <v>0.81999999999999795</v>
       </c>
       <c r="M51">
-        <v>0.84330000000000005</v>
+        <v>0.84330000000000505</v>
       </c>
       <c r="N51">
         <v>0.83960000000000001</v>
@@ -3214,7 +3215,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P51"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3234,28 +3235,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -3281,31 +3282,31 @@
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I2">
-        <v>0.88400000000000001</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="J2">
         <v>0.95409999999999995</v>
@@ -3331,31 +3332,31 @@
     </row>
     <row r="3" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I3">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0.95409999999999995</v>
@@ -3364,7 +3365,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L3">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M3">
         <v>0.93289999999999995</v>
@@ -3381,19 +3382,19 @@
     </row>
     <row r="4" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -3402,10 +3403,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I4">
-        <v>0.61599999999999999</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0.95409999999999995</v>
@@ -3414,7 +3415,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L4">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M4">
         <v>0.93289999999999995</v>
@@ -3431,31 +3432,31 @@
     </row>
     <row r="5" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5">
-        <v>0.65200000000000002</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0.95409999999999995</v>
@@ -3464,7 +3465,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L5">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M5">
         <v>0.93289999999999995</v>
@@ -3481,28 +3482,28 @@
     </row>
     <row r="6" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -3514,7 +3515,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L6">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M6">
         <v>0.93289999999999995</v>
@@ -3531,31 +3532,31 @@
     </row>
     <row r="7" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>0.72399999999999998</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0.95409999999999995</v>
@@ -3564,7 +3565,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L7">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M7">
         <v>0.93289999999999995</v>
@@ -3581,19 +3582,19 @@
     </row>
     <row r="8" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -3602,10 +3603,10 @@
         <v>4</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I8">
-        <v>0.76600000000000001</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0.95409999999999995</v>
@@ -3614,7 +3615,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L8">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M8">
         <v>0.93289999999999995</v>
@@ -3631,7 +3632,7 @@
     </row>
     <row r="9" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -3640,13 +3641,13 @@
         <v>3</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -3655,7 +3656,7 @@
         <v>16</v>
       </c>
       <c r="I9">
-        <v>0.98199999999999998</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0.95409999999999995</v>
@@ -3664,7 +3665,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L9">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M9">
         <v>0.93289999999999995</v>
@@ -3681,31 +3682,31 @@
     </row>
     <row r="10" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="J10">
         <v>0.95409999999999995</v>
@@ -3714,7 +3715,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L10">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M10">
         <v>0.93289999999999995</v>
@@ -3731,31 +3732,31 @@
     </row>
     <row r="11" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I11">
-        <v>0.78800000000000003</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="J11">
         <v>0.95409999999999995</v>
@@ -3764,7 +3765,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L11">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M11">
         <v>0.93289999999999995</v>
@@ -3781,10 +3782,10 @@
     </row>
     <row r="12" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -3793,19 +3794,19 @@
         <v>3</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I12">
-        <v>0.76600000000000001</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="J12">
         <v>0.95409999999999995</v>
@@ -3814,7 +3815,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L12">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M12">
         <v>0.93289999999999995</v>
@@ -3831,28 +3832,28 @@
     </row>
     <row r="13" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -3864,7 +3865,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L13">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M13">
         <v>0.93289999999999995</v>
@@ -3881,31 +3882,31 @@
     </row>
     <row r="14" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I14">
-        <v>0.55200000000000005</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0.95409999999999995</v>
@@ -3914,7 +3915,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L14">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M14">
         <v>0.93289999999999995</v>
@@ -3931,31 +3932,31 @@
     </row>
     <row r="15" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
       </c>
       <c r="I15">
-        <v>0.94399999999999995</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0.95409999999999995</v>
@@ -3964,7 +3965,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L15">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M15">
         <v>0.93289999999999995</v>
@@ -3981,28 +3982,28 @@
     </row>
     <row r="16" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -4014,7 +4015,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L16">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M16">
         <v>0.93289999999999995</v>
@@ -4031,31 +4032,31 @@
     </row>
     <row r="17" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I17">
-        <v>0.69399999999999995</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0.95409999999999995</v>
@@ -4064,7 +4065,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L17">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M17">
         <v>0.93289999999999995</v>
@@ -4081,7 +4082,7 @@
     </row>
     <row r="18" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="B18">
         <v>3</v>
@@ -4093,19 +4094,19 @@
         <v>3</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I18">
-        <v>0.78200000000000003</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="J18">
         <v>0.95409999999999995</v>
@@ -4114,7 +4115,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L18">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M18">
         <v>0.93289999999999995</v>
@@ -4131,13 +4132,13 @@
     </row>
     <row r="19" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -4146,13 +4147,13 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -4164,7 +4165,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L19">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M19">
         <v>0.93289999999999995</v>
@@ -4181,31 +4182,31 @@
     </row>
     <row r="20" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I20">
-        <v>0.72199999999999998</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>0.95409999999999995</v>
@@ -4214,7 +4215,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L20">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M20">
         <v>0.93289999999999995</v>
@@ -4231,31 +4232,31 @@
     </row>
     <row r="21" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H21" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I21">
-        <v>0.88400000000000001</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0.95409999999999995</v>
@@ -4264,7 +4265,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L21">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M21">
         <v>0.93289999999999995</v>
@@ -4281,7 +4282,7 @@
     </row>
     <row r="22" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -4290,22 +4291,22 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="J22">
         <v>0.95409999999999995</v>
@@ -4314,7 +4315,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L22">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M22">
         <v>0.93289999999999995</v>
@@ -4331,31 +4332,31 @@
     </row>
     <row r="23" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23">
         <v>3</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
       </c>
       <c r="I23">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>0.95409999999999995</v>
@@ -4364,7 +4365,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L23">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M23">
         <v>0.93289999999999995</v>
@@ -4381,25 +4382,25 @@
     </row>
     <row r="24" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -4414,7 +4415,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L24">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M24">
         <v>0.93289999999999995</v>
@@ -4431,31 +4432,31 @@
     </row>
     <row r="25" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
       </c>
       <c r="I25">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0.95409999999999995</v>
@@ -4464,7 +4465,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L25">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M25">
         <v>0.93289999999999995</v>
@@ -4481,31 +4482,31 @@
     </row>
     <row r="26" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
       </c>
       <c r="I26">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>0.95409999999999995</v>
@@ -4514,7 +4515,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L26">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M26">
         <v>0.93289999999999995</v>
@@ -4531,31 +4532,31 @@
     </row>
     <row r="27" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
       </c>
       <c r="I27">
-        <v>0.69599999999999995</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>0.95409999999999995</v>
@@ -4564,7 +4565,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L27">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M27">
         <v>0.93289999999999995</v>
@@ -4581,19 +4582,19 @@
     </row>
     <row r="28" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28">
         <v>4</v>
@@ -4602,10 +4603,10 @@
         <v>4</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I28">
-        <v>0.59199999999999997</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>0.95409999999999995</v>
@@ -4614,7 +4615,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L28">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M28">
         <v>0.93289999999999995</v>
@@ -4631,28 +4632,28 @@
     </row>
     <row r="29" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -4664,7 +4665,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L29">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M29">
         <v>0.93289999999999995</v>
@@ -4681,7 +4682,7 @@
     </row>
     <row r="30" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -4690,22 +4691,22 @@
         <v>4</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30">
         <v>3</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I30">
-        <v>0.94399999999999995</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0.95409999999999995</v>
@@ -4714,7 +4715,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L30">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M30">
         <v>0.93289999999999995</v>
@@ -4731,7 +4732,7 @@
     </row>
     <row r="31" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -4746,16 +4747,16 @@
         <v>5</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I31">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0.95409999999999995</v>
@@ -4764,7 +4765,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L31">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M31">
         <v>0.93289999999999995</v>
@@ -4781,19 +4782,19 @@
     </row>
     <row r="32" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C32">
         <v>4</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>4</v>
@@ -4802,7 +4803,7 @@
         <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -4814,7 +4815,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L32">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M32">
         <v>0.93289999999999995</v>
@@ -4831,25 +4832,25 @@
     </row>
     <row r="33" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -4864,7 +4865,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L33">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M33">
         <v>0.93289999999999995</v>
@@ -4881,13 +4882,13 @@
     </row>
     <row r="34" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -4896,16 +4897,16 @@
         <v>4</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I34">
-        <v>0.82799999999999996</v>
+        <v>0.91400000000000003</v>
       </c>
       <c r="J34">
         <v>0.95409999999999995</v>
@@ -4914,7 +4915,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L34">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M34">
         <v>0.93289999999999995</v>
@@ -4931,10 +4932,10 @@
     </row>
     <row r="35" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -4943,19 +4944,19 @@
         <v>5</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H35" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I35">
-        <v>0.57599999999999996</v>
+        <v>1</v>
       </c>
       <c r="J35">
         <v>0.95409999999999995</v>
@@ -4964,7 +4965,7 @@
         <v>0.90810000000000002</v>
       </c>
       <c r="L35">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M35">
         <v>0.93289999999999995</v>
@@ -4981,40 +4982,40 @@
     </row>
     <row r="36" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I36">
-        <v>0.996</v>
+        <v>0.83399999999999996</v>
       </c>
       <c r="J36">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999895</v>
       </c>
       <c r="K36">
         <v>0.90810000000000002</v>
       </c>
       <c r="L36">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M36">
         <v>0.93289999999999995</v>
@@ -5031,7 +5032,7 @@
     </row>
     <row r="37" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -5040,31 +5041,31 @@
         <v>2</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="J37">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999895</v>
       </c>
       <c r="K37">
         <v>0.90810000000000002</v>
       </c>
       <c r="L37">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M37">
         <v>0.93289999999999995</v>
@@ -5081,7 +5082,7 @@
     </row>
     <row r="38" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -5090,13 +5091,13 @@
         <v>3</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -5105,16 +5106,16 @@
         <v>16</v>
       </c>
       <c r="I38">
-        <v>0.95599999999999996</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999895</v>
       </c>
       <c r="K38">
         <v>0.90810000000000002</v>
       </c>
       <c r="L38">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M38">
         <v>0.93289999999999995</v>
@@ -5131,40 +5132,40 @@
     </row>
     <row r="39" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H39" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I39">
-        <v>0.88400000000000001</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999895</v>
       </c>
       <c r="K39">
         <v>0.90810000000000002</v>
       </c>
       <c r="L39">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M39">
         <v>0.93289999999999995</v>
@@ -5181,40 +5182,40 @@
     </row>
     <row r="40" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H40" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I40">
         <v>1</v>
       </c>
       <c r="J40">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999895</v>
       </c>
       <c r="K40">
         <v>0.90810000000000002</v>
       </c>
       <c r="L40">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M40">
         <v>0.93289999999999995</v>
@@ -5231,13 +5232,13 @@
     </row>
     <row r="41" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -5246,25 +5247,25 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I41">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999795</v>
       </c>
       <c r="K41">
         <v>0.90810000000000002</v>
       </c>
       <c r="L41">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M41">
         <v>0.93289999999999995</v>
@@ -5281,7 +5282,7 @@
     </row>
     <row r="42" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="B42">
         <v>4</v>
@@ -5290,31 +5291,31 @@
         <v>4</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H42" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I42">
-        <v>0.71399999999999997</v>
+        <v>1</v>
       </c>
       <c r="J42">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999795</v>
       </c>
       <c r="K42">
         <v>0.90810000000000002</v>
       </c>
       <c r="L42">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M42">
         <v>0.93289999999999995</v>
@@ -5331,40 +5332,40 @@
     </row>
     <row r="43" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I43">
         <v>1</v>
       </c>
       <c r="J43">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999795</v>
       </c>
       <c r="K43">
         <v>0.90810000000000002</v>
       </c>
       <c r="L43">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M43">
         <v>0.93289999999999995</v>
@@ -5381,40 +5382,40 @@
     </row>
     <row r="44" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
       </c>
       <c r="I44">
-        <v>0.99199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J44">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999795</v>
       </c>
       <c r="K44">
         <v>0.90810000000000002</v>
       </c>
       <c r="L44">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M44">
         <v>0.93289999999999995</v>
@@ -5431,40 +5432,40 @@
     </row>
     <row r="45" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45">
         <v>4</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
       </c>
       <c r="I45">
-        <v>0.59199999999999997</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="J45">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999795</v>
       </c>
       <c r="K45">
         <v>0.90810000000000002</v>
       </c>
       <c r="L45">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M45">
         <v>0.93289999999999995</v>
@@ -5481,40 +5482,40 @@
     </row>
     <row r="46" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46">
         <v>4</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I46">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999795</v>
       </c>
       <c r="K46">
         <v>0.90810000000000002</v>
       </c>
       <c r="L46">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M46">
         <v>0.93289999999999995</v>
@@ -5531,16 +5532,16 @@
     </row>
     <row r="47" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47">
         <v>5</v>
@@ -5552,19 +5553,19 @@
         <v>4</v>
       </c>
       <c r="H47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I47">
         <v>1</v>
       </c>
       <c r="J47">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999795</v>
       </c>
       <c r="K47">
         <v>0.90810000000000002</v>
       </c>
       <c r="L47">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M47">
         <v>0.93289999999999995</v>
@@ -5581,40 +5582,40 @@
     </row>
     <row r="48" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H48" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I48">
         <v>1</v>
       </c>
       <c r="J48">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999695</v>
       </c>
       <c r="K48">
         <v>0.90810000000000002</v>
       </c>
       <c r="L48">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M48">
         <v>0.93289999999999995</v>
@@ -5631,16 +5632,16 @@
     </row>
     <row r="49" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49">
         <v>4</v>
@@ -5652,19 +5653,19 @@
         <v>4</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I49">
         <v>1</v>
       </c>
       <c r="J49">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999695</v>
       </c>
       <c r="K49">
         <v>0.90810000000000002</v>
       </c>
       <c r="L49">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M49">
         <v>0.93289999999999995</v>
@@ -5681,40 +5682,40 @@
     </row>
     <row r="50" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50">
         <v>4</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H50" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I50">
-        <v>0.78400000000000003</v>
+        <v>1</v>
       </c>
       <c r="J50">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999695</v>
       </c>
       <c r="K50">
         <v>0.90810000000000002</v>
       </c>
       <c r="L50">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M50">
         <v>0.93289999999999995</v>
@@ -5731,7 +5732,7 @@
     </row>
     <row r="51" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="B51">
         <v>3</v>
@@ -5743,28 +5744,28 @@
         <v>2</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
       </c>
       <c r="I51">
-        <v>0.65200000000000002</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>0.95409999999999995</v>
+        <v>0.95409999999999695</v>
       </c>
       <c r="K51">
         <v>0.90810000000000002</v>
       </c>
       <c r="L51">
-        <v>0.97529999999999994</v>
+        <v>0.97430000000000005</v>
       </c>
       <c r="M51">
         <v>0.93289999999999995</v>
@@ -5785,7 +5786,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R50"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5799,13 +5800,13 @@
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -5829,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="L1" t="s">
         <v>8</v>
@@ -5855,13 +5856,13 @@
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -5882,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -5911,13 +5912,13 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -5938,7 +5939,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -5967,13 +5968,13 @@
     </row>
     <row r="4" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -5994,7 +5995,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K4">
         <v>0.97599999999999998</v>
@@ -6023,13 +6024,13 @@
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -6050,7 +6051,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K5">
         <v>0.68</v>
@@ -6079,13 +6080,13 @@
     </row>
     <row r="6" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -6106,7 +6107,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K6">
         <v>0.68</v>
@@ -6135,13 +6136,13 @@
     </row>
     <row r="7" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -6162,7 +6163,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -6191,13 +6192,13 @@
     </row>
     <row r="8" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -6218,7 +6219,7 @@
         <v>5</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -6247,13 +6248,13 @@
     </row>
     <row r="9" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -6274,7 +6275,7 @@
         <v>3</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K9">
         <v>0.58399999999999996</v>
@@ -6303,13 +6304,13 @@
     </row>
     <row r="10" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -6330,7 +6331,7 @@
         <v>3</v>
       </c>
       <c r="J10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10">
         <v>0.58399999999999996</v>
@@ -6359,13 +6360,13 @@
     </row>
     <row r="11" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -6386,7 +6387,7 @@
         <v>3</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K11">
         <v>0.58399999999999996</v>
@@ -6415,13 +6416,13 @@
     </row>
     <row r="12" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -6442,7 +6443,7 @@
         <v>3</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K12">
         <v>0.99199999999999999</v>
@@ -6471,13 +6472,13 @@
     </row>
     <row r="13" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -6498,7 +6499,7 @@
         <v>3</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K13">
         <v>0.99199999999999999</v>
@@ -6527,13 +6528,13 @@
     </row>
     <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -6554,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K14">
         <v>0.90200000000000002</v>
@@ -6583,13 +6584,13 @@
     </row>
     <row r="15" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -6610,7 +6611,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K15">
         <v>0.90200000000000002</v>
@@ -6639,13 +6640,13 @@
     </row>
     <row r="16" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -6666,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K16">
         <v>0.82199999999999995</v>
@@ -6695,13 +6696,13 @@
     </row>
     <row r="17" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -6722,7 +6723,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K17">
         <v>0.82199999999999995</v>
@@ -6751,13 +6752,13 @@
     </row>
     <row r="18" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -6778,7 +6779,7 @@
         <v>5</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -6807,13 +6808,13 @@
     </row>
     <row r="19" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -6834,7 +6835,7 @@
         <v>5</v>
       </c>
       <c r="J19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -6863,13 +6864,13 @@
     </row>
     <row r="20" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -6890,7 +6891,7 @@
         <v>3</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K20">
         <v>0.83599999999999997</v>
@@ -6919,13 +6920,13 @@
     </row>
     <row r="21" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -6946,7 +6947,7 @@
         <v>3</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K21">
         <v>0.83599999999999997</v>
@@ -6975,13 +6976,13 @@
     </row>
     <row r="22" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -7002,7 +7003,7 @@
         <v>3</v>
       </c>
       <c r="J22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -7031,13 +7032,13 @@
     </row>
     <row r="23" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -7058,7 +7059,7 @@
         <v>3</v>
       </c>
       <c r="J23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -7087,13 +7088,13 @@
     </row>
     <row r="24" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -7114,7 +7115,7 @@
         <v>5</v>
       </c>
       <c r="J24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K24">
         <v>0.98799999999999999</v>
@@ -7143,13 +7144,13 @@
     </row>
     <row r="25" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -7170,7 +7171,7 @@
         <v>5</v>
       </c>
       <c r="J25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K25">
         <v>0.98799999999999999</v>
@@ -7199,13 +7200,13 @@
     </row>
     <row r="26" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -7226,7 +7227,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K26">
         <v>0.98799999999999999</v>
@@ -7255,13 +7256,13 @@
     </row>
     <row r="27" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -7282,7 +7283,7 @@
         <v>5</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K27">
         <v>0.98799999999999999</v>
@@ -7311,13 +7312,13 @@
     </row>
     <row r="28" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -7338,7 +7339,7 @@
         <v>3</v>
       </c>
       <c r="J28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K28">
         <v>0.996</v>
@@ -7367,13 +7368,13 @@
     </row>
     <row r="29" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -7394,7 +7395,7 @@
         <v>3</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K29">
         <v>0.996</v>
@@ -7423,13 +7424,13 @@
     </row>
     <row r="30" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -7450,7 +7451,7 @@
         <v>3</v>
       </c>
       <c r="J30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -7479,13 +7480,13 @@
     </row>
     <row r="31" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -7506,7 +7507,7 @@
         <v>3</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -7535,13 +7536,13 @@
     </row>
     <row r="32" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -7562,7 +7563,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -7591,13 +7592,13 @@
     </row>
     <row r="33" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D33">
         <v>3</v>
@@ -7618,7 +7619,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -7647,13 +7648,13 @@
     </row>
     <row r="34" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -7674,7 +7675,7 @@
         <v>3</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K34">
         <v>0.99399999999999999</v>
@@ -7703,13 +7704,13 @@
     </row>
     <row r="35" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -7730,7 +7731,7 @@
         <v>3</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K35">
         <v>0.99399999999999999</v>
@@ -7759,13 +7760,13 @@
     </row>
     <row r="36" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D36">
         <v>3</v>
@@ -7786,7 +7787,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K36">
         <v>0.998</v>
@@ -7815,13 +7816,13 @@
     </row>
     <row r="37" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -7842,7 +7843,7 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K37">
         <v>0.998</v>
@@ -7871,13 +7872,13 @@
     </row>
     <row r="38" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -7898,7 +7899,7 @@
         <v>2</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K38">
         <v>0.99399999999999999</v>
@@ -7927,13 +7928,13 @@
     </row>
     <row r="39" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -7954,7 +7955,7 @@
         <v>2</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K39">
         <v>0.99399999999999999</v>
@@ -7983,13 +7984,13 @@
     </row>
     <row r="40" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -8010,7 +8011,7 @@
         <v>3</v>
       </c>
       <c r="J40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K40">
         <v>0.89200000000000002</v>
@@ -8039,13 +8040,13 @@
     </row>
     <row r="41" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -8066,7 +8067,7 @@
         <v>3</v>
       </c>
       <c r="J41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K41">
         <v>0.89200000000000002</v>
@@ -8095,13 +8096,13 @@
     </row>
     <row r="42" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D42">
         <v>3</v>
@@ -8122,7 +8123,7 @@
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K42">
         <v>0.91</v>
@@ -8151,13 +8152,13 @@
     </row>
     <row r="43" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -8178,7 +8179,7 @@
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K43">
         <v>0.91</v>
@@ -8207,13 +8208,13 @@
     </row>
     <row r="44" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -8234,7 +8235,7 @@
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K44">
         <v>0.84</v>
@@ -8263,13 +8264,13 @@
     </row>
     <row r="45" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -8290,7 +8291,7 @@
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K45">
         <v>0.84</v>
@@ -8319,34 +8320,34 @@
     </row>
     <row r="46" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46" t="s">
         <v>16</v>
-      </c>
-      <c r="D46">
-        <v>3</v>
-      </c>
-      <c r="E46">
-        <v>4</v>
-      </c>
-      <c r="F46">
-        <v>2</v>
-      </c>
-      <c r="G46">
-        <v>3</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46">
-        <v>1</v>
-      </c>
-      <c r="J46" t="s">
-        <v>18</v>
       </c>
       <c r="K46">
         <v>0.56599999999999995</v>
@@ -8375,34 +8376,34 @@
     </row>
     <row r="47" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47">
+        <v>3</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47" t="s">
         <v>16</v>
-      </c>
-      <c r="D47">
-        <v>3</v>
-      </c>
-      <c r="E47">
-        <v>4</v>
-      </c>
-      <c r="F47">
-        <v>2</v>
-      </c>
-      <c r="G47">
-        <v>3</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
-      </c>
-      <c r="J47" t="s">
-        <v>18</v>
       </c>
       <c r="K47">
         <v>0.56599999999999995</v>
@@ -8431,34 +8432,34 @@
     </row>
     <row r="48" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48" t="s">
         <v>16</v>
-      </c>
-      <c r="D48">
-        <v>3</v>
-      </c>
-      <c r="E48">
-        <v>4</v>
-      </c>
-      <c r="F48">
-        <v>2</v>
-      </c>
-      <c r="G48">
-        <v>3</v>
-      </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48">
-        <v>1</v>
-      </c>
-      <c r="J48" t="s">
-        <v>18</v>
       </c>
       <c r="K48">
         <v>0.56599999999999995</v>
@@ -8487,34 +8488,34 @@
     </row>
     <row r="49" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="G49">
+        <v>3</v>
+      </c>
+      <c r="H49">
+        <v>3</v>
+      </c>
+      <c r="I49">
+        <v>5</v>
+      </c>
+      <c r="J49" t="s">
         <v>16</v>
-      </c>
-      <c r="D49">
-        <v>2</v>
-      </c>
-      <c r="E49">
-        <v>3</v>
-      </c>
-      <c r="F49">
-        <v>3</v>
-      </c>
-      <c r="G49">
-        <v>3</v>
-      </c>
-      <c r="H49">
-        <v>3</v>
-      </c>
-      <c r="I49">
-        <v>5</v>
-      </c>
-      <c r="J49" t="s">
-        <v>18</v>
       </c>
       <c r="K49">
         <v>0.99399999999999999</v>
@@ -8543,34 +8544,34 @@
     </row>
     <row r="50" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>4</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50" t="s">
         <v>16</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50">
-        <v>4</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-      <c r="H50">
-        <v>2</v>
-      </c>
-      <c r="I50">
-        <v>2</v>
-      </c>
-      <c r="J50" t="s">
-        <v>18</v>
       </c>
       <c r="K50">
         <v>0.98599999999999999</v>
@@ -8603,7 +8604,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R50"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8616,37 +8617,37 @@
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="H1" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="I1" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="J1" t="s">
         <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="L1" t="s">
         <v>8</v>
@@ -8672,13 +8673,13 @@
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -8699,7 +8700,7 @@
         <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2">
         <v>0.996</v>
@@ -8728,13 +8729,13 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -8755,7 +8756,7 @@
         <v>4</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K3">
         <v>0.996</v>
@@ -8784,13 +8785,13 @@
     </row>
     <row r="4" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -8811,7 +8812,7 @@
         <v>2</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -8840,13 +8841,13 @@
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -8867,7 +8868,7 @@
         <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -8896,13 +8897,13 @@
     </row>
     <row r="6" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -8923,7 +8924,7 @@
         <v>4</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -8952,13 +8953,13 @@
     </row>
     <row r="7" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -8979,7 +8980,7 @@
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K7">
         <v>0.97799999999999998</v>
@@ -9008,13 +9009,13 @@
     </row>
     <row r="8" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -9035,7 +9036,7 @@
         <v>4</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K8">
         <v>0.97799999999999998</v>
@@ -9064,13 +9065,13 @@
     </row>
     <row r="9" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -9091,7 +9092,7 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -9120,13 +9121,13 @@
     </row>
     <row r="10" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -9147,7 +9148,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -9176,13 +9177,13 @@
     </row>
     <row r="11" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -9203,7 +9204,7 @@
         <v>5</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -9232,13 +9233,13 @@
     </row>
     <row r="12" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -9259,7 +9260,7 @@
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -9288,13 +9289,13 @@
     </row>
     <row r="13" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -9315,7 +9316,7 @@
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -9344,13 +9345,13 @@
     </row>
     <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -9371,7 +9372,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -9400,13 +9401,13 @@
     </row>
     <row r="15" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -9427,7 +9428,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -9456,13 +9457,13 @@
     </row>
     <row r="16" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -9483,7 +9484,7 @@
         <v>2</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -9512,13 +9513,13 @@
     </row>
     <row r="17" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -9539,7 +9540,7 @@
         <v>2</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -9568,34 +9569,34 @@
     </row>
     <row r="18" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+      <c r="J18" t="s">
         <v>16</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18">
-        <v>3</v>
-      </c>
-      <c r="H18">
-        <v>3</v>
-      </c>
-      <c r="I18">
-        <v>4</v>
-      </c>
-      <c r="J18" t="s">
-        <v>18</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -9624,34 +9625,34 @@
     </row>
     <row r="19" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <v>4</v>
+      </c>
+      <c r="J19" t="s">
         <v>16</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-      <c r="H19">
-        <v>3</v>
-      </c>
-      <c r="I19">
-        <v>4</v>
-      </c>
-      <c r="J19" t="s">
-        <v>18</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -9680,13 +9681,13 @@
     </row>
     <row r="20" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -9707,7 +9708,7 @@
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -9736,13 +9737,13 @@
     </row>
     <row r="21" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -9763,7 +9764,7 @@
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -9792,13 +9793,13 @@
     </row>
     <row r="22" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -9819,7 +9820,7 @@
         <v>3</v>
       </c>
       <c r="J22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K22">
         <v>0.98199999999999998</v>
@@ -9848,13 +9849,13 @@
     </row>
     <row r="23" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -9875,7 +9876,7 @@
         <v>3</v>
       </c>
       <c r="J23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K23">
         <v>0.98199999999999998</v>
@@ -9904,34 +9905,34 @@
     </row>
     <row r="24" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
         <v>16</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
-      <c r="F24">
-        <v>3</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-      <c r="H24">
-        <v>2</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24" t="s">
-        <v>18</v>
       </c>
       <c r="K24">
         <v>0.93200000000000005</v>
@@ -9960,34 +9961,34 @@
     </row>
     <row r="25" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" t="s">
         <v>16</v>
-      </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
-      <c r="F25">
-        <v>3</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25">
-        <v>2</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25" t="s">
-        <v>18</v>
       </c>
       <c r="K25">
         <v>0.93200000000000005</v>
@@ -10016,34 +10017,34 @@
     </row>
     <row r="26" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" t="s">
         <v>16</v>
-      </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-      <c r="H26">
-        <v>2</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26" t="s">
-        <v>18</v>
       </c>
       <c r="K26">
         <v>0.93200000000000005</v>
@@ -10072,34 +10073,34 @@
     </row>
     <row r="27" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
         <v>16</v>
-      </c>
-      <c r="D27">
-        <v>2</v>
-      </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
-      <c r="F27">
-        <v>3</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-      <c r="H27">
-        <v>2</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27" t="s">
-        <v>18</v>
       </c>
       <c r="K27">
         <v>0.93200000000000005</v>
@@ -10128,13 +10129,13 @@
     </row>
     <row r="28" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -10155,7 +10156,7 @@
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -10184,13 +10185,13 @@
     </row>
     <row r="29" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -10211,7 +10212,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -10240,13 +10241,13 @@
     </row>
     <row r="30" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -10267,7 +10268,7 @@
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -10296,13 +10297,13 @@
     </row>
     <row r="31" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -10323,7 +10324,7 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -10352,13 +10353,13 @@
     </row>
     <row r="32" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -10379,7 +10380,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -10408,13 +10409,13 @@
     </row>
     <row r="33" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -10435,7 +10436,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -10464,13 +10465,13 @@
     </row>
     <row r="34" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -10491,7 +10492,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -10520,13 +10521,13 @@
     </row>
     <row r="35" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -10547,7 +10548,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -10576,13 +10577,13 @@
     </row>
     <row r="36" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -10603,7 +10604,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -10632,13 +10633,13 @@
     </row>
     <row r="37" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -10659,7 +10660,7 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -10688,13 +10689,13 @@
     </row>
     <row r="38" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -10715,7 +10716,7 @@
         <v>2</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -10744,13 +10745,13 @@
     </row>
     <row r="39" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -10771,7 +10772,7 @@
         <v>2</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -10800,13 +10801,13 @@
     </row>
     <row r="40" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -10827,7 +10828,7 @@
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K40">
         <v>1</v>
@@ -10856,13 +10857,13 @@
     </row>
     <row r="41" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -10883,7 +10884,7 @@
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -10912,13 +10913,13 @@
     </row>
     <row r="42" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -10939,7 +10940,7 @@
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K42">
         <v>1</v>
@@ -10968,13 +10969,13 @@
     </row>
     <row r="43" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -10995,7 +10996,7 @@
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -11024,13 +11025,13 @@
     </row>
     <row r="44" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -11051,7 +11052,7 @@
         <v>3</v>
       </c>
       <c r="J44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K44">
         <v>0.998</v>
@@ -11080,13 +11081,13 @@
     </row>
     <row r="45" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -11107,7 +11108,7 @@
         <v>3</v>
       </c>
       <c r="J45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K45">
         <v>0.998</v>
@@ -11136,13 +11137,13 @@
     </row>
     <row r="46" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -11163,7 +11164,7 @@
         <v>2</v>
       </c>
       <c r="J46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K46">
         <v>0.95599999999999996</v>
@@ -11192,13 +11193,13 @@
     </row>
     <row r="47" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -11219,7 +11220,7 @@
         <v>2</v>
       </c>
       <c r="J47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K47">
         <v>0.95599999999999996</v>
@@ -11248,13 +11249,13 @@
     </row>
     <row r="48" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -11275,7 +11276,7 @@
         <v>2</v>
       </c>
       <c r="J48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K48">
         <v>0.95599999999999996</v>
@@ -11304,13 +11305,13 @@
     </row>
     <row r="49" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -11331,7 +11332,7 @@
         <v>2</v>
       </c>
       <c r="J49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K49">
         <v>1</v>
@@ -11360,34 +11361,34 @@
     </row>
     <row r="50" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50" t="s">
         <v>16</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
-      </c>
-      <c r="J50" t="s">
-        <v>18</v>
       </c>
       <c r="K50">
         <v>1</v>
